--- a/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B8D6221-5C0A-4A65-925D-68B38438B63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{642860FF-C343-4DDD-A785-287DA3D13BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1445,10 +1445,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,FaD,WaP,FaP,SaP,RaP,SaD,RaD</t>
+    <t>FaP,SaP,RaD,WaP,WaD,SaD,RaP,FaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,WaP,RaN,FaN,FaP,SaP</t>
+    <t>RaN,WaP,FaP,SaP,FaN,RaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24888,7 +24888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF391E9-9D64-4B25-A3DA-0953CA2B70A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAF06D6-720F-4DF8-9BF6-EE24FD04F32C}">
   <dimension ref="A9:AN146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25226,7 +25226,7 @@
         <v>151</v>
       </c>
       <c r="AM13">
-        <v>0.37540092593393276</v>
+        <v>0.37540092593393282</v>
       </c>
       <c r="AN13" t="s">
         <v>448</v>
@@ -25276,7 +25276,7 @@
         <v>151</v>
       </c>
       <c r="AM14">
-        <v>0.39233333333333326</v>
+        <v>0.39233333333333337</v>
       </c>
       <c r="AN14" t="s">
         <v>448</v>
@@ -25476,7 +25476,7 @@
         <v>151</v>
       </c>
       <c r="AM18">
-        <v>0.33209166666666667</v>
+        <v>0.33209166666666662</v>
       </c>
       <c r="AN18" t="s">
         <v>448</v>
@@ -25576,7 +25576,7 @@
         <v>151</v>
       </c>
       <c r="AM20">
-        <v>0.33509166666666662</v>
+        <v>0.33509166666666673</v>
       </c>
       <c r="AN20" t="s">
         <v>448</v>
@@ -25626,7 +25626,7 @@
         <v>151</v>
       </c>
       <c r="AM21">
-        <v>0.32289166666666669</v>
+        <v>0.32289166666666663</v>
       </c>
       <c r="AN21" t="s">
         <v>448</v>
@@ -25676,7 +25676,7 @@
         <v>151</v>
       </c>
       <c r="AM22">
-        <v>0.43725000000000008</v>
+        <v>0.43724999999999997</v>
       </c>
       <c r="AN22" t="s">
         <v>448</v>
@@ -25776,7 +25776,7 @@
         <v>151</v>
       </c>
       <c r="AM24">
-        <v>0.33310833333333334</v>
+        <v>0.33310833333333328</v>
       </c>
       <c r="AN24" t="s">
         <v>448</v>
@@ -25826,7 +25826,7 @@
         <v>151</v>
       </c>
       <c r="AM25">
-        <v>0.38650000000000001</v>
+        <v>0.38650000000000007</v>
       </c>
       <c r="AN25" t="s">
         <v>448</v>
@@ -25876,7 +25876,7 @@
         <v>151</v>
       </c>
       <c r="AM26">
-        <v>0.4544333333333333</v>
+        <v>0.45443333333333341</v>
       </c>
       <c r="AN26" t="s">
         <v>448</v>
@@ -25976,7 +25976,7 @@
         <v>151</v>
       </c>
       <c r="AM28">
-        <v>0.44177500000000003</v>
+        <v>0.44177499999999997</v>
       </c>
       <c r="AN28" t="s">
         <v>448</v>
@@ -26126,7 +26126,7 @@
         <v>151</v>
       </c>
       <c r="AM31">
-        <v>0.44190833333333335</v>
+        <v>0.4419083333333334</v>
       </c>
       <c r="AN31" t="s">
         <v>448</v>
@@ -26276,7 +26276,7 @@
         <v>151</v>
       </c>
       <c r="AM34">
-        <v>0.43522500000000003</v>
+        <v>0.43522499999999997</v>
       </c>
       <c r="AN34" t="s">
         <v>448</v>
@@ -26376,7 +26376,7 @@
         <v>151</v>
       </c>
       <c r="AM36">
-        <v>0.3874333333333333</v>
+        <v>0.38743333333333335</v>
       </c>
       <c r="AN36" t="s">
         <v>448</v>
@@ -26526,7 +26526,7 @@
         <v>151</v>
       </c>
       <c r="AM39">
-        <v>0.37857499999999994</v>
+        <v>0.37857500000000005</v>
       </c>
       <c r="AN39" t="s">
         <v>448</v>
@@ -29116,7 +29116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A671A507-BCA7-43B8-AB6D-6A665EDA478A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D466E6D9-DB78-4BDE-A96C-942BDA9B9C7F}">
   <dimension ref="A9:AN1642"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29846,7 +29846,7 @@
         <v>452</v>
       </c>
       <c r="AM17">
-        <v>0.50458966641045067</v>
+        <v>0.50458966641045055</v>
       </c>
       <c r="AN17" t="s">
         <v>448</v>
@@ -30006,7 +30006,7 @@
         <v>449</v>
       </c>
       <c r="AM19">
-        <v>0.34749890723128757</v>
+        <v>0.34749890723128751</v>
       </c>
       <c r="AN19" t="s">
         <v>448</v>
@@ -30086,7 +30086,7 @@
         <v>451</v>
       </c>
       <c r="AM20">
-        <v>0.36364634589612016</v>
+        <v>0.36364634589612027</v>
       </c>
       <c r="AN20" t="s">
         <v>448</v>
@@ -30364,7 +30364,7 @@
         <v>451</v>
       </c>
       <c r="AM24">
-        <v>0.35673333333333335</v>
+        <v>0.35673333333333329</v>
       </c>
       <c r="AN24" t="s">
         <v>448</v>
@@ -30600,7 +30600,7 @@
         <v>451</v>
       </c>
       <c r="AM28">
-        <v>0.27929999999999994</v>
+        <v>0.27929999999999999</v>
       </c>
       <c r="AN28" t="s">
         <v>448</v>
@@ -30836,7 +30836,7 @@
         <v>451</v>
       </c>
       <c r="AM32">
-        <v>0.28550000000000003</v>
+        <v>0.28549999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>448</v>
@@ -31204,7 +31204,7 @@
         <v>449</v>
       </c>
       <c r="AM39">
-        <v>0.37786666666666663</v>
+        <v>0.37786666666666674</v>
       </c>
       <c r="AN39" t="s">
         <v>448</v>
@@ -31604,7 +31604,7 @@
         <v>449</v>
       </c>
       <c r="AM47">
-        <v>0.35653333333333337</v>
+        <v>0.35653333333333331</v>
       </c>
       <c r="AN47" t="s">
         <v>448</v>
@@ -31654,7 +31654,7 @@
         <v>451</v>
       </c>
       <c r="AM48">
-        <v>0.29123333333333329</v>
+        <v>0.29123333333333334</v>
       </c>
       <c r="AN48" t="s">
         <v>448</v>
@@ -31854,7 +31854,7 @@
         <v>451</v>
       </c>
       <c r="AM52">
-        <v>0.27396666666666669</v>
+        <v>0.27396666666666664</v>
       </c>
       <c r="AN52" t="s">
         <v>448</v>
@@ -31904,7 +31904,7 @@
         <v>452</v>
       </c>
       <c r="AM53">
-        <v>0.40429999999999994</v>
+        <v>0.40430000000000005</v>
       </c>
       <c r="AN53" t="s">
         <v>448</v>
@@ -32304,7 +32304,7 @@
         <v>452</v>
       </c>
       <c r="AM61">
-        <v>0.4864666666666666</v>
+        <v>0.48646666666666666</v>
       </c>
       <c r="AN61" t="s">
         <v>448</v>
@@ -33454,7 +33454,7 @@
         <v>451</v>
       </c>
       <c r="AM84">
-        <v>0.38696666666666668</v>
+        <v>0.38696666666666663</v>
       </c>
       <c r="AN84" t="s">
         <v>448</v>
@@ -33854,7 +33854,7 @@
         <v>451</v>
       </c>
       <c r="AM92">
-        <v>0.38786666666666664</v>
+        <v>0.38786666666666675</v>
       </c>
       <c r="AN92" t="s">
         <v>448</v>
@@ -34254,7 +34254,7 @@
         <v>451</v>
       </c>
       <c r="AM100">
-        <v>0.34893333333333337</v>
+        <v>0.34893333333333332</v>
       </c>
       <c r="AN100" t="s">
         <v>448</v>
@@ -34804,7 +34804,7 @@
         <v>449</v>
       </c>
       <c r="AM111">
-        <v>0.43383333333333329</v>
+        <v>0.43383333333333335</v>
       </c>
       <c r="AN111" t="s">
         <v>448</v>
@@ -35004,7 +35004,7 @@
         <v>449</v>
       </c>
       <c r="AM115">
-        <v>0.42910000000000004</v>
+        <v>0.42909999999999998</v>
       </c>
       <c r="AN115" t="s">
         <v>448</v>
@@ -35104,7 +35104,7 @@
         <v>452</v>
       </c>
       <c r="AM117">
-        <v>0.5063333333333333</v>
+        <v>0.50633333333333341</v>
       </c>
       <c r="AN117" t="s">
         <v>448</v>
@@ -35504,7 +35504,7 @@
         <v>452</v>
       </c>
       <c r="AM125">
-        <v>0.49640000000000012</v>
+        <v>0.49640000000000001</v>
       </c>
       <c r="AN125" t="s">
         <v>448</v>

--- a/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{642860FF-C343-4DDD-A785-287DA3D13BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8ED79FB-E2F7-4752-A84A-731A5075C69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1445,10 +1445,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaD,WaP,WaD,SaD,RaP,FaD</t>
+    <t>RaP,FaD,FaP,SaP,SaD,WaD,WaP,RaD</t>
   </si>
   <si>
-    <t>RaN,WaP,FaP,SaP,FaN,RaP,SaN,WaN</t>
+    <t>SaN,WaN,RaP,FaP,SaP,WaP,RaN,FaN</t>
   </si>
 </sst>
 </file>
@@ -24888,7 +24888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAF06D6-720F-4DF8-9BF6-EE24FD04F32C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D0C245-1890-4990-85F3-DDCFDDB9B76C}">
   <dimension ref="A9:AN146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25176,7 +25176,7 @@
         <v>151</v>
       </c>
       <c r="AM12">
-        <v>0.38306266416910179</v>
+        <v>0.38306266416910173</v>
       </c>
       <c r="AN12" t="s">
         <v>448</v>
@@ -25226,7 +25226,7 @@
         <v>151</v>
       </c>
       <c r="AM13">
-        <v>0.37540092593393282</v>
+        <v>0.37540092593393276</v>
       </c>
       <c r="AN13" t="s">
         <v>448</v>
@@ -25276,7 +25276,7 @@
         <v>151</v>
       </c>
       <c r="AM14">
-        <v>0.39233333333333337</v>
+        <v>0.39233333333333326</v>
       </c>
       <c r="AN14" t="s">
         <v>448</v>
@@ -25326,7 +25326,7 @@
         <v>151</v>
       </c>
       <c r="AM15">
-        <v>0.32144166666666668</v>
+        <v>0.32144166666666663</v>
       </c>
       <c r="AN15" t="s">
         <v>448</v>
@@ -25476,7 +25476,7 @@
         <v>151</v>
       </c>
       <c r="AM18">
-        <v>0.33209166666666662</v>
+        <v>0.33209166666666673</v>
       </c>
       <c r="AN18" t="s">
         <v>448</v>
@@ -25576,7 +25576,7 @@
         <v>151</v>
       </c>
       <c r="AM20">
-        <v>0.33509166666666673</v>
+        <v>0.33509166666666662</v>
       </c>
       <c r="AN20" t="s">
         <v>448</v>
@@ -25776,7 +25776,7 @@
         <v>151</v>
       </c>
       <c r="AM24">
-        <v>0.33310833333333328</v>
+        <v>0.33310833333333334</v>
       </c>
       <c r="AN24" t="s">
         <v>448</v>
@@ -25826,7 +25826,7 @@
         <v>151</v>
       </c>
       <c r="AM25">
-        <v>0.38650000000000007</v>
+        <v>0.38650000000000001</v>
       </c>
       <c r="AN25" t="s">
         <v>448</v>
@@ -25976,7 +25976,7 @@
         <v>151</v>
       </c>
       <c r="AM28">
-        <v>0.44177499999999997</v>
+        <v>0.44177500000000003</v>
       </c>
       <c r="AN28" t="s">
         <v>448</v>
@@ -26076,7 +26076,7 @@
         <v>151</v>
       </c>
       <c r="AM30">
-        <v>0.43517500000000003</v>
+        <v>0.43517499999999992</v>
       </c>
       <c r="AN30" t="s">
         <v>448</v>
@@ -26526,7 +26526,7 @@
         <v>151</v>
       </c>
       <c r="AM39">
-        <v>0.37857500000000005</v>
+        <v>0.37857499999999994</v>
       </c>
       <c r="AN39" t="s">
         <v>448</v>
@@ -29116,7 +29116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D466E6D9-DB78-4BDE-A96C-942BDA9B9C7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DDCD6D-6E84-40EB-BB47-0F8E8F636E9D}">
   <dimension ref="A9:AN1642"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29345,7 +29345,7 @@
         <v>449</v>
       </c>
       <c r="AM11">
-        <v>0.49795736213049863</v>
+        <v>0.49795736213049852</v>
       </c>
       <c r="AN11" t="s">
         <v>448</v>
@@ -29846,7 +29846,7 @@
         <v>452</v>
       </c>
       <c r="AM17">
-        <v>0.50458966641045055</v>
+        <v>0.50458966641045067</v>
       </c>
       <c r="AN17" t="s">
         <v>448</v>
@@ -30086,7 +30086,7 @@
         <v>451</v>
       </c>
       <c r="AM20">
-        <v>0.36364634589612027</v>
+        <v>0.36364634589612016</v>
       </c>
       <c r="AN20" t="s">
         <v>448</v>
@@ -30246,7 +30246,7 @@
         <v>454</v>
       </c>
       <c r="AM22">
-        <v>0.27374366247873677</v>
+        <v>0.27374366247873683</v>
       </c>
       <c r="AN22" t="s">
         <v>448</v>
@@ -30364,7 +30364,7 @@
         <v>451</v>
       </c>
       <c r="AM24">
-        <v>0.35673333333333329</v>
+        <v>0.35673333333333335</v>
       </c>
       <c r="AN24" t="s">
         <v>448</v>
@@ -30600,7 +30600,7 @@
         <v>451</v>
       </c>
       <c r="AM28">
-        <v>0.27929999999999999</v>
+        <v>0.27929999999999994</v>
       </c>
       <c r="AN28" t="s">
         <v>448</v>
@@ -30836,7 +30836,7 @@
         <v>451</v>
       </c>
       <c r="AM32">
-        <v>0.28549999999999998</v>
+        <v>0.28550000000000003</v>
       </c>
       <c r="AN32" t="s">
         <v>448</v>
@@ -31204,7 +31204,7 @@
         <v>449</v>
       </c>
       <c r="AM39">
-        <v>0.37786666666666674</v>
+        <v>0.37786666666666663</v>
       </c>
       <c r="AN39" t="s">
         <v>448</v>
@@ -31604,7 +31604,7 @@
         <v>449</v>
       </c>
       <c r="AM47">
-        <v>0.35653333333333331</v>
+        <v>0.35653333333333337</v>
       </c>
       <c r="AN47" t="s">
         <v>448</v>
@@ -31654,7 +31654,7 @@
         <v>451</v>
       </c>
       <c r="AM48">
-        <v>0.29123333333333334</v>
+        <v>0.29123333333333329</v>
       </c>
       <c r="AN48" t="s">
         <v>448</v>
@@ -31854,7 +31854,7 @@
         <v>451</v>
       </c>
       <c r="AM52">
-        <v>0.27396666666666664</v>
+        <v>0.27396666666666669</v>
       </c>
       <c r="AN52" t="s">
         <v>448</v>
@@ -31904,7 +31904,7 @@
         <v>452</v>
       </c>
       <c r="AM53">
-        <v>0.40430000000000005</v>
+        <v>0.40429999999999994</v>
       </c>
       <c r="AN53" t="s">
         <v>448</v>
@@ -32304,7 +32304,7 @@
         <v>452</v>
       </c>
       <c r="AM61">
-        <v>0.48646666666666666</v>
+        <v>0.4864666666666666</v>
       </c>
       <c r="AN61" t="s">
         <v>448</v>
@@ -32754,7 +32754,7 @@
         <v>454</v>
       </c>
       <c r="AM70">
-        <v>0.29060000000000002</v>
+        <v>0.29059999999999997</v>
       </c>
       <c r="AN70" t="s">
         <v>448</v>
@@ -33204,7 +33204,7 @@
         <v>449</v>
       </c>
       <c r="AM79">
-        <v>0.49590000000000001</v>
+        <v>0.49589999999999995</v>
       </c>
       <c r="AN79" t="s">
         <v>448</v>
@@ -33404,7 +33404,7 @@
         <v>449</v>
       </c>
       <c r="AM83">
-        <v>0.47756666666666669</v>
+        <v>0.47756666666666664</v>
       </c>
       <c r="AN83" t="s">
         <v>448</v>
@@ -33454,7 +33454,7 @@
         <v>451</v>
       </c>
       <c r="AM84">
-        <v>0.38696666666666663</v>
+        <v>0.38696666666666668</v>
       </c>
       <c r="AN84" t="s">
         <v>448</v>
@@ -33554,7 +33554,7 @@
         <v>454</v>
       </c>
       <c r="AM86">
-        <v>0.3066666666666667</v>
+        <v>0.30666666666666664</v>
       </c>
       <c r="AN86" t="s">
         <v>448</v>
@@ -33604,7 +33604,7 @@
         <v>449</v>
       </c>
       <c r="AM87">
-        <v>0.49076666666666674</v>
+        <v>0.49076666666666663</v>
       </c>
       <c r="AN87" t="s">
         <v>448</v>
@@ -33854,7 +33854,7 @@
         <v>451</v>
       </c>
       <c r="AM92">
-        <v>0.38786666666666675</v>
+        <v>0.38786666666666664</v>
       </c>
       <c r="AN92" t="s">
         <v>448</v>
@@ -34254,7 +34254,7 @@
         <v>451</v>
       </c>
       <c r="AM100">
-        <v>0.34893333333333332</v>
+        <v>0.34893333333333337</v>
       </c>
       <c r="AN100" t="s">
         <v>448</v>
@@ -34804,7 +34804,7 @@
         <v>449</v>
       </c>
       <c r="AM111">
-        <v>0.43383333333333335</v>
+        <v>0.43383333333333329</v>
       </c>
       <c r="AN111" t="s">
         <v>448</v>
@@ -35004,7 +35004,7 @@
         <v>449</v>
       </c>
       <c r="AM115">
-        <v>0.42909999999999998</v>
+        <v>0.42910000000000004</v>
       </c>
       <c r="AN115" t="s">
         <v>448</v>
@@ -35104,7 +35104,7 @@
         <v>452</v>
       </c>
       <c r="AM117">
-        <v>0.50633333333333341</v>
+        <v>0.5063333333333333</v>
       </c>
       <c r="AN117" t="s">
         <v>448</v>
@@ -35154,7 +35154,7 @@
         <v>454</v>
       </c>
       <c r="AM118">
-        <v>0.25706666666666667</v>
+        <v>0.25706666666666672</v>
       </c>
       <c r="AN118" t="s">
         <v>448</v>
@@ -35504,7 +35504,7 @@
         <v>452</v>
       </c>
       <c r="AM125">
-        <v>0.49640000000000001</v>
+        <v>0.49640000000000012</v>
       </c>
       <c r="AN125" t="s">
         <v>448</v>

--- a/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8ED79FB-E2F7-4752-A84A-731A5075C69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93036AE8-DE44-45C7-BC35-6E9B16A17D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1445,10 +1445,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaP,FaD,FaP,SaP,SaD,WaD,WaP,RaD</t>
+    <t>SaD,FaD,RaD,WaD,RaP,WaP,FaP,SaP</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,FaP,SaP,WaP,RaN,FaN</t>
+    <t>FaP,SaP,RaP,RaN,WaP,FaN,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24888,7 +24888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D0C245-1890-4990-85F3-DDCFDDB9B76C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7EB87EA-D24F-43C1-BADB-B4B6E28C7B0B}">
   <dimension ref="A9:AN146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25176,7 +25176,7 @@
         <v>151</v>
       </c>
       <c r="AM12">
-        <v>0.38306266416910173</v>
+        <v>0.38306266416910179</v>
       </c>
       <c r="AN12" t="s">
         <v>448</v>
@@ -25276,7 +25276,7 @@
         <v>151</v>
       </c>
       <c r="AM14">
-        <v>0.39233333333333326</v>
+        <v>0.39233333333333337</v>
       </c>
       <c r="AN14" t="s">
         <v>448</v>
@@ -25326,7 +25326,7 @@
         <v>151</v>
       </c>
       <c r="AM15">
-        <v>0.32144166666666663</v>
+        <v>0.32144166666666668</v>
       </c>
       <c r="AN15" t="s">
         <v>448</v>
@@ -25426,7 +25426,7 @@
         <v>151</v>
       </c>
       <c r="AM17">
-        <v>0.33303333333333335</v>
+        <v>0.33303333333333329</v>
       </c>
       <c r="AN17" t="s">
         <v>448</v>
@@ -25476,7 +25476,7 @@
         <v>151</v>
       </c>
       <c r="AM18">
-        <v>0.33209166666666673</v>
+        <v>0.33209166666666667</v>
       </c>
       <c r="AN18" t="s">
         <v>448</v>
@@ -25576,7 +25576,7 @@
         <v>151</v>
       </c>
       <c r="AM20">
-        <v>0.33509166666666662</v>
+        <v>0.33509166666666673</v>
       </c>
       <c r="AN20" t="s">
         <v>448</v>
@@ -25676,7 +25676,7 @@
         <v>151</v>
       </c>
       <c r="AM22">
-        <v>0.43724999999999997</v>
+        <v>0.43725000000000008</v>
       </c>
       <c r="AN22" t="s">
         <v>448</v>
@@ -26076,7 +26076,7 @@
         <v>151</v>
       </c>
       <c r="AM30">
-        <v>0.43517499999999992</v>
+        <v>0.43517500000000003</v>
       </c>
       <c r="AN30" t="s">
         <v>448</v>
@@ -26126,7 +26126,7 @@
         <v>151</v>
       </c>
       <c r="AM31">
-        <v>0.4419083333333334</v>
+        <v>0.44190833333333335</v>
       </c>
       <c r="AN31" t="s">
         <v>448</v>
@@ -26276,7 +26276,7 @@
         <v>151</v>
       </c>
       <c r="AM34">
-        <v>0.43522499999999997</v>
+        <v>0.43522500000000003</v>
       </c>
       <c r="AN34" t="s">
         <v>448</v>
@@ -26476,7 +26476,7 @@
         <v>151</v>
       </c>
       <c r="AM38">
-        <v>0.37768333333333332</v>
+        <v>0.37768333333333337</v>
       </c>
       <c r="AN38" t="s">
         <v>448</v>
@@ -29116,7 +29116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DDCD6D-6E84-40EB-BB47-0F8E8F636E9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8601B372-15A8-47E6-8EF6-AB3DDFF5332C}">
   <dimension ref="A9:AN1642"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29345,7 +29345,7 @@
         <v>449</v>
       </c>
       <c r="AM11">
-        <v>0.49795736213049852</v>
+        <v>0.49795736213049863</v>
       </c>
       <c r="AN11" t="s">
         <v>448</v>
@@ -29846,7 +29846,7 @@
         <v>452</v>
       </c>
       <c r="AM17">
-        <v>0.50458966641045067</v>
+        <v>0.50458966641045055</v>
       </c>
       <c r="AN17" t="s">
         <v>448</v>
@@ -30006,7 +30006,7 @@
         <v>449</v>
       </c>
       <c r="AM19">
-        <v>0.34749890723128751</v>
+        <v>0.34749890723128757</v>
       </c>
       <c r="AN19" t="s">
         <v>448</v>
@@ -30086,7 +30086,7 @@
         <v>451</v>
       </c>
       <c r="AM20">
-        <v>0.36364634589612016</v>
+        <v>0.36364634589612027</v>
       </c>
       <c r="AN20" t="s">
         <v>448</v>
@@ -30246,7 +30246,7 @@
         <v>454</v>
       </c>
       <c r="AM22">
-        <v>0.27374366247873683</v>
+        <v>0.27374366247873677</v>
       </c>
       <c r="AN22" t="s">
         <v>448</v>
@@ -30364,7 +30364,7 @@
         <v>451</v>
       </c>
       <c r="AM24">
-        <v>0.35673333333333335</v>
+        <v>0.35673333333333329</v>
       </c>
       <c r="AN24" t="s">
         <v>448</v>
@@ -30600,7 +30600,7 @@
         <v>451</v>
       </c>
       <c r="AM28">
-        <v>0.27929999999999994</v>
+        <v>0.27929999999999999</v>
       </c>
       <c r="AN28" t="s">
         <v>448</v>
@@ -30718,7 +30718,7 @@
         <v>454</v>
       </c>
       <c r="AM30">
-        <v>0.23506666666666665</v>
+        <v>0.23506666666666667</v>
       </c>
       <c r="AN30" t="s">
         <v>448</v>
@@ -30836,7 +30836,7 @@
         <v>451</v>
       </c>
       <c r="AM32">
-        <v>0.28550000000000003</v>
+        <v>0.28549999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>448</v>
@@ -31654,7 +31654,7 @@
         <v>451</v>
       </c>
       <c r="AM48">
-        <v>0.29123333333333329</v>
+        <v>0.29123333333333334</v>
       </c>
       <c r="AN48" t="s">
         <v>448</v>
@@ -31854,7 +31854,7 @@
         <v>451</v>
       </c>
       <c r="AM52">
-        <v>0.27396666666666669</v>
+        <v>0.27396666666666664</v>
       </c>
       <c r="AN52" t="s">
         <v>448</v>
@@ -31904,7 +31904,7 @@
         <v>452</v>
       </c>
       <c r="AM53">
-        <v>0.40429999999999994</v>
+        <v>0.40430000000000005</v>
       </c>
       <c r="AN53" t="s">
         <v>448</v>
@@ -31954,7 +31954,7 @@
         <v>454</v>
       </c>
       <c r="AM54">
-        <v>0.2341</v>
+        <v>0.23409999999999997</v>
       </c>
       <c r="AN54" t="s">
         <v>448</v>
@@ -32304,7 +32304,7 @@
         <v>452</v>
       </c>
       <c r="AM61">
-        <v>0.4864666666666666</v>
+        <v>0.48646666666666666</v>
       </c>
       <c r="AN61" t="s">
         <v>448</v>
@@ -32754,7 +32754,7 @@
         <v>454</v>
       </c>
       <c r="AM70">
-        <v>0.29059999999999997</v>
+        <v>0.29060000000000002</v>
       </c>
       <c r="AN70" t="s">
         <v>448</v>
@@ -33204,7 +33204,7 @@
         <v>449</v>
       </c>
       <c r="AM79">
-        <v>0.49589999999999995</v>
+        <v>0.49590000000000001</v>
       </c>
       <c r="AN79" t="s">
         <v>448</v>
@@ -33404,7 +33404,7 @@
         <v>449</v>
       </c>
       <c r="AM83">
-        <v>0.47756666666666664</v>
+        <v>0.47756666666666669</v>
       </c>
       <c r="AN83" t="s">
         <v>448</v>
@@ -33454,7 +33454,7 @@
         <v>451</v>
       </c>
       <c r="AM84">
-        <v>0.38696666666666668</v>
+        <v>0.38696666666666663</v>
       </c>
       <c r="AN84" t="s">
         <v>448</v>
@@ -33554,7 +33554,7 @@
         <v>454</v>
       </c>
       <c r="AM86">
-        <v>0.30666666666666664</v>
+        <v>0.3066666666666667</v>
       </c>
       <c r="AN86" t="s">
         <v>448</v>
@@ -33604,7 +33604,7 @@
         <v>449</v>
       </c>
       <c r="AM87">
-        <v>0.49076666666666663</v>
+        <v>0.49076666666666674</v>
       </c>
       <c r="AN87" t="s">
         <v>448</v>
@@ -33854,7 +33854,7 @@
         <v>451</v>
       </c>
       <c r="AM92">
-        <v>0.38786666666666664</v>
+        <v>0.38786666666666675</v>
       </c>
       <c r="AN92" t="s">
         <v>448</v>
@@ -34254,7 +34254,7 @@
         <v>451</v>
       </c>
       <c r="AM100">
-        <v>0.34893333333333337</v>
+        <v>0.34893333333333332</v>
       </c>
       <c r="AN100" t="s">
         <v>448</v>
@@ -35104,7 +35104,7 @@
         <v>452</v>
       </c>
       <c r="AM117">
-        <v>0.5063333333333333</v>
+        <v>0.50633333333333341</v>
       </c>
       <c r="AN117" t="s">
         <v>448</v>
@@ -35154,7 +35154,7 @@
         <v>454</v>
       </c>
       <c r="AM118">
-        <v>0.25706666666666672</v>
+        <v>0.25706666666666667</v>
       </c>
       <c r="AN118" t="s">
         <v>448</v>
@@ -35504,7 +35504,7 @@
         <v>452</v>
       </c>
       <c r="AM125">
-        <v>0.49640000000000012</v>
+        <v>0.49640000000000001</v>
       </c>
       <c r="AN125" t="s">
         <v>448</v>

--- a/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F30A3AFE-9F8D-4D65-9875-839A6D930AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{604474BA-9DCD-4B9D-8BA6-5BEE1CB9AD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1484,10 +1484,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,WaP,RaD,SaD,WaD,FaD</t>
+    <t>WaD,FaD,SaD,WaP,RaD,RaP,FaP,SaP</t>
   </si>
   <si>
-    <t>WaP,RaN,FaN,SaN,WaN,FaP,SaP,RaP</t>
+    <t>RaP,FaP,SaP,RaN,SaN,WaN,FaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24939,7 +24939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765E2A9B-C2FF-4815-8B36-E965F97DE339}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DB760A-B153-4B43-8018-8358AFCAD78B}">
   <dimension ref="A9:AN146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25477,7 +25477,7 @@
         <v>152</v>
       </c>
       <c r="AM17">
-        <v>0.33303333333333329</v>
+        <v>0.33303333333333335</v>
       </c>
       <c r="AN17" t="s">
         <v>449</v>
@@ -25577,7 +25577,7 @@
         <v>152</v>
       </c>
       <c r="AM19">
-        <v>0.44320833333333326</v>
+        <v>0.44320833333333337</v>
       </c>
       <c r="AN19" t="s">
         <v>449</v>
@@ -25927,7 +25927,7 @@
         <v>152</v>
       </c>
       <c r="AM26">
-        <v>0.4544333333333333</v>
+        <v>0.45443333333333341</v>
       </c>
       <c r="AN26" t="s">
         <v>449</v>
@@ -26227,7 +26227,7 @@
         <v>152</v>
       </c>
       <c r="AM32">
-        <v>0.43754999999999994</v>
+        <v>0.43755000000000005</v>
       </c>
       <c r="AN32" t="s">
         <v>449</v>
@@ -26327,7 +26327,7 @@
         <v>152</v>
       </c>
       <c r="AM34">
-        <v>0.43522499999999997</v>
+        <v>0.43522500000000003</v>
       </c>
       <c r="AN34" t="s">
         <v>449</v>
@@ -26527,7 +26527,7 @@
         <v>152</v>
       </c>
       <c r="AM38">
-        <v>0.37768333333333337</v>
+        <v>0.37768333333333332</v>
       </c>
       <c r="AN38" t="s">
         <v>449</v>
@@ -26577,7 +26577,7 @@
         <v>152</v>
       </c>
       <c r="AM39">
-        <v>0.37857499999999994</v>
+        <v>0.37857500000000005</v>
       </c>
       <c r="AN39" t="s">
         <v>449</v>
@@ -29167,7 +29167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A25FFE-9E10-4C16-BB90-44E68B90E700}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6988B439-24A4-4E1F-B0BE-F97464FFA7C8}">
   <dimension ref="A9:AN1642"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29396,7 +29396,7 @@
         <v>450</v>
       </c>
       <c r="AM11">
-        <v>0.49795736213049863</v>
+        <v>0.49795736213049852</v>
       </c>
       <c r="AN11" t="s">
         <v>449</v>
@@ -29574,7 +29574,7 @@
         <v>453</v>
       </c>
       <c r="AM13">
-        <v>0.55211626377820133</v>
+        <v>0.55211626377820122</v>
       </c>
       <c r="AN13" t="s">
         <v>449</v>
@@ -30297,7 +30297,7 @@
         <v>455</v>
       </c>
       <c r="AM22">
-        <v>0.27374366247873677</v>
+        <v>0.27374366247873683</v>
       </c>
       <c r="AN22" t="s">
         <v>449</v>
@@ -30769,7 +30769,7 @@
         <v>455</v>
       </c>
       <c r="AM30">
-        <v>0.23506666666666667</v>
+        <v>0.23506666666666665</v>
       </c>
       <c r="AN30" t="s">
         <v>449</v>
@@ -30946,7 +30946,7 @@
         <v>453</v>
       </c>
       <c r="AM33">
-        <v>0.44189999999999996</v>
+        <v>0.44190000000000002</v>
       </c>
       <c r="AN33" t="s">
         <v>449</v>
@@ -31255,7 +31255,7 @@
         <v>450</v>
       </c>
       <c r="AM39">
-        <v>0.37786666666666674</v>
+        <v>0.37786666666666663</v>
       </c>
       <c r="AN39" t="s">
         <v>449</v>
@@ -31555,7 +31555,7 @@
         <v>453</v>
       </c>
       <c r="AM45">
-        <v>0.59456666666666669</v>
+        <v>0.59456666666666658</v>
       </c>
       <c r="AN45" t="s">
         <v>449</v>
@@ -31655,7 +31655,7 @@
         <v>450</v>
       </c>
       <c r="AM47">
-        <v>0.35653333333333331</v>
+        <v>0.35653333333333337</v>
       </c>
       <c r="AN47" t="s">
         <v>449</v>
@@ -32005,7 +32005,7 @@
         <v>455</v>
       </c>
       <c r="AM54">
-        <v>0.23409999999999997</v>
+        <v>0.2341</v>
       </c>
       <c r="AN54" t="s">
         <v>449</v>
@@ -32805,7 +32805,7 @@
         <v>455</v>
       </c>
       <c r="AM70">
-        <v>0.29060000000000002</v>
+        <v>0.29059999999999997</v>
       </c>
       <c r="AN70" t="s">
         <v>449</v>
@@ -33255,7 +33255,7 @@
         <v>450</v>
       </c>
       <c r="AM79">
-        <v>0.49590000000000001</v>
+        <v>0.49589999999999995</v>
       </c>
       <c r="AN79" t="s">
         <v>449</v>
@@ -33455,7 +33455,7 @@
         <v>450</v>
       </c>
       <c r="AM83">
-        <v>0.47756666666666669</v>
+        <v>0.47756666666666664</v>
       </c>
       <c r="AN83" t="s">
         <v>449</v>
@@ -33605,7 +33605,7 @@
         <v>455</v>
       </c>
       <c r="AM86">
-        <v>0.3066666666666667</v>
+        <v>0.30666666666666664</v>
       </c>
       <c r="AN86" t="s">
         <v>449</v>
@@ -33655,7 +33655,7 @@
         <v>450</v>
       </c>
       <c r="AM87">
-        <v>0.49076666666666674</v>
+        <v>0.49076666666666663</v>
       </c>
       <c r="AN87" t="s">
         <v>449</v>
@@ -33755,7 +33755,7 @@
         <v>453</v>
       </c>
       <c r="AM89">
-        <v>0.54199999999999993</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="AN89" t="s">
         <v>449</v>
@@ -34855,7 +34855,7 @@
         <v>450</v>
       </c>
       <c r="AM111">
-        <v>0.43383333333333335</v>
+        <v>0.43383333333333329</v>
       </c>
       <c r="AN111" t="s">
         <v>449</v>
@@ -35055,7 +35055,7 @@
         <v>450</v>
       </c>
       <c r="AM115">
-        <v>0.42909999999999998</v>
+        <v>0.42910000000000004</v>
       </c>
       <c r="AN115" t="s">
         <v>449</v>
@@ -35205,7 +35205,7 @@
         <v>455</v>
       </c>
       <c r="AM118">
-        <v>0.25706666666666667</v>
+        <v>0.25706666666666672</v>
       </c>
       <c r="AN118" t="s">
         <v>449</v>

--- a/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_CHN/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{604474BA-9DCD-4B9D-8BA6-5BEE1CB9AD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D324EC7-76FC-4B18-A65E-1CBCADF6A4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1484,10 +1484,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,FaD,SaD,WaP,RaD,RaP,FaP,SaP</t>
+    <t>WaP,WaD,FaP,SaP,FaD,RaD,SaD,RaP</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,RaN,SaN,WaN,FaN,WaP</t>
+    <t>SaN,WaN,RaN,FaN,WaP,RaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24939,7 +24939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DB760A-B153-4B43-8018-8358AFCAD78B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8D2F05-0D2F-4A2E-A881-30BAEED9E809}">
   <dimension ref="A9:AN146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25227,7 +25227,7 @@
         <v>152</v>
       </c>
       <c r="AM12">
-        <v>0.38306266416910179</v>
+        <v>0.3830626641691019</v>
       </c>
       <c r="AN12" t="s">
         <v>449</v>
@@ -25577,7 +25577,7 @@
         <v>152</v>
       </c>
       <c r="AM19">
-        <v>0.44320833333333337</v>
+        <v>0.44320833333333326</v>
       </c>
       <c r="AN19" t="s">
         <v>449</v>
@@ -25627,7 +25627,7 @@
         <v>152</v>
       </c>
       <c r="AM20">
-        <v>0.33509166666666673</v>
+        <v>0.33509166666666662</v>
       </c>
       <c r="AN20" t="s">
         <v>449</v>
@@ -25877,7 +25877,7 @@
         <v>152</v>
       </c>
       <c r="AM25">
-        <v>0.38650000000000001</v>
+        <v>0.38650000000000007</v>
       </c>
       <c r="AN25" t="s">
         <v>449</v>
@@ -25927,7 +25927,7 @@
         <v>152</v>
       </c>
       <c r="AM26">
-        <v>0.45443333333333341</v>
+        <v>0.4544333333333333</v>
       </c>
       <c r="AN26" t="s">
         <v>449</v>
@@ -26027,7 +26027,7 @@
         <v>152</v>
       </c>
       <c r="AM28">
-        <v>0.44177499999999997</v>
+        <v>0.44177500000000003</v>
       </c>
       <c r="AN28" t="s">
         <v>449</v>
@@ -26077,7 +26077,7 @@
         <v>152</v>
       </c>
       <c r="AM29">
-        <v>0.44534999999999997</v>
+        <v>0.44535000000000008</v>
       </c>
       <c r="AN29" t="s">
         <v>449</v>
@@ -26127,7 +26127,7 @@
         <v>152</v>
       </c>
       <c r="AM30">
-        <v>0.43517500000000003</v>
+        <v>0.43517500000000009</v>
       </c>
       <c r="AN30" t="s">
         <v>449</v>
@@ -26277,7 +26277,7 @@
         <v>152</v>
       </c>
       <c r="AM33">
-        <v>0.38585833333333336</v>
+        <v>0.38585833333333341</v>
       </c>
       <c r="AN33" t="s">
         <v>449</v>
@@ -26427,7 +26427,7 @@
         <v>152</v>
       </c>
       <c r="AM36">
-        <v>0.38743333333333335</v>
+        <v>0.3874333333333333</v>
       </c>
       <c r="AN36" t="s">
         <v>449</v>
@@ -26577,7 +26577,7 @@
         <v>152</v>
       </c>
       <c r="AM39">
-        <v>0.37857500000000005</v>
+        <v>0.37857499999999994</v>
       </c>
       <c r="AN39" t="s">
         <v>449</v>
@@ -29167,7 +29167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6988B439-24A4-4E1F-B0BE-F97464FFA7C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1960D350-FCDA-4DDB-8994-2A7E20ADF772}">
   <dimension ref="A9:AN1642"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29396,7 +29396,7 @@
         <v>450</v>
       </c>
       <c r="AM11">
-        <v>0.49795736213049852</v>
+        <v>0.49795736213049863</v>
       </c>
       <c r="AN11" t="s">
         <v>449</v>
@@ -29574,7 +29574,7 @@
         <v>453</v>
       </c>
       <c r="AM13">
-        <v>0.55211626377820122</v>
+        <v>0.55211626377820133</v>
       </c>
       <c r="AN13" t="s">
         <v>449</v>
@@ -30137,7 +30137,7 @@
         <v>452</v>
       </c>
       <c r="AM20">
-        <v>0.36364634589612027</v>
+        <v>0.36364634589612016</v>
       </c>
       <c r="AN20" t="s">
         <v>449</v>
@@ -30297,7 +30297,7 @@
         <v>455</v>
       </c>
       <c r="AM22">
-        <v>0.27374366247873683</v>
+        <v>0.27374366247873677</v>
       </c>
       <c r="AN22" t="s">
         <v>449</v>
@@ -30651,7 +30651,7 @@
         <v>452</v>
       </c>
       <c r="AM28">
-        <v>0.27929999999999999</v>
+        <v>0.27929999999999994</v>
       </c>
       <c r="AN28" t="s">
         <v>449</v>
@@ -30946,7 +30946,7 @@
         <v>453</v>
       </c>
       <c r="AM33">
-        <v>0.44190000000000002</v>
+        <v>0.44189999999999996</v>
       </c>
       <c r="AN33" t="s">
         <v>449</v>
@@ -31255,7 +31255,7 @@
         <v>450</v>
       </c>
       <c r="AM39">
-        <v>0.37786666666666663</v>
+        <v>0.37786666666666674</v>
       </c>
       <c r="AN39" t="s">
         <v>449</v>
@@ -31555,7 +31555,7 @@
         <v>453</v>
       </c>
       <c r="AM45">
-        <v>0.59456666666666658</v>
+        <v>0.59456666666666669</v>
       </c>
       <c r="AN45" t="s">
         <v>449</v>
@@ -31655,7 +31655,7 @@
         <v>450</v>
       </c>
       <c r="AM47">
-        <v>0.35653333333333337</v>
+        <v>0.35653333333333331</v>
       </c>
       <c r="AN47" t="s">
         <v>449</v>
@@ -31905,7 +31905,7 @@
         <v>452</v>
       </c>
       <c r="AM52">
-        <v>0.27396666666666664</v>
+        <v>0.27396666666666669</v>
       </c>
       <c r="AN52" t="s">
         <v>449</v>
@@ -32805,7 +32805,7 @@
         <v>455</v>
       </c>
       <c r="AM70">
-        <v>0.29059999999999997</v>
+        <v>0.29060000000000002</v>
       </c>
       <c r="AN70" t="s">
         <v>449</v>
@@ -32905,7 +32905,7 @@
         <v>452</v>
       </c>
       <c r="AM72">
-        <v>0.40286666666666665</v>
+        <v>0.40286666666666671</v>
       </c>
       <c r="AN72" t="s">
         <v>449</v>
@@ -33255,7 +33255,7 @@
         <v>450</v>
       </c>
       <c r="AM79">
-        <v>0.49589999999999995</v>
+        <v>0.49590000000000001</v>
       </c>
       <c r="AN79" t="s">
         <v>449</v>
@@ -33455,7 +33455,7 @@
         <v>450</v>
       </c>
       <c r="AM83">
-        <v>0.47756666666666664</v>
+        <v>0.47756666666666669</v>
       </c>
       <c r="AN83" t="s">
         <v>449</v>
@@ -33605,7 +33605,7 @@
         <v>455</v>
       </c>
       <c r="AM86">
-        <v>0.30666666666666664</v>
+        <v>0.3066666666666667</v>
       </c>
       <c r="AN86" t="s">
         <v>449</v>
@@ -33655,7 +33655,7 @@
         <v>450</v>
       </c>
       <c r="AM87">
-        <v>0.49076666666666663</v>
+        <v>0.49076666666666674</v>
       </c>
       <c r="AN87" t="s">
         <v>449</v>
@@ -33755,7 +33755,7 @@
         <v>453</v>
       </c>
       <c r="AM89">
-        <v>0.54200000000000004</v>
+        <v>0.54199999999999993</v>
       </c>
       <c r="AN89" t="s">
         <v>449</v>
@@ -34505,7 +34505,7 @@
         <v>452</v>
       </c>
       <c r="AM104">
-        <v>0.34830000000000005</v>
+        <v>0.3483</v>
       </c>
       <c r="AN104" t="s">
         <v>449</v>
@@ -34855,7 +34855,7 @@
         <v>450</v>
       </c>
       <c r="AM111">
-        <v>0.43383333333333329</v>
+        <v>0.43383333333333335</v>
       </c>
       <c r="AN111" t="s">
         <v>449</v>
@@ -35055,7 +35055,7 @@
         <v>450</v>
       </c>
       <c r="AM115">
-        <v>0.42910000000000004</v>
+        <v>0.42909999999999998</v>
       </c>
       <c r="AN115" t="s">
         <v>449</v>
@@ -35205,7 +35205,7 @@
         <v>455</v>
       </c>
       <c r="AM118">
-        <v>0.25706666666666672</v>
+        <v>0.25706666666666667</v>
       </c>
       <c r="AN118" t="s">
         <v>449</v>
